--- a/examples/outputs/Birgo RR Exhibits - Hertel Homesv08.31.26.xlsx
+++ b/examples/outputs/Birgo RR Exhibits - Hertel Homesv08.31.26.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Unit Mix based on # of Beds" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Pres. Rent Roll" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="OneLineRR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Source" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="#0\ &quot;Units&quot;"/>
     <numFmt numFmtId="165" formatCode="#\ &quot;Units&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0\ &quot;SF&quot;"/>
@@ -36,6 +37,8 @@
     <numFmt numFmtId="176" formatCode="mm\/dd\/yyyy"/>
     <numFmt numFmtId="177" formatCode="0.0"/>
     <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="180" formatCode="[$-409]m\/d\/yy"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -153,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -387,6 +390,10 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -26192,4 +26199,9088 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V180"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.5546875" customWidth="1" min="1" max="1"/>
+    <col width="1.33203125" customWidth="1" min="2" max="2"/>
+    <col width="3.44140625" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="4.21875" customWidth="1" min="6" max="6"/>
+    <col width="10.21875" customWidth="1" min="7" max="7"/>
+    <col width="1.5546875" customWidth="1" min="8" max="8"/>
+    <col width="5.88671875" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8.77734375" customWidth="1" min="12" max="12"/>
+    <col width="1.44140625" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="8.44140625" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="8.44140625" customWidth="1" min="17" max="17"/>
+    <col width="7.5546875" customWidth="1" min="18" max="18"/>
+    <col width="5.5546875" customWidth="1" min="19" max="19"/>
+    <col width="1.33203125" customWidth="1" min="21" max="21"/>
+    <col width="4.21875" customWidth="1" min="22" max="22"/>
+    <col width="5.6640625" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="87" t="inlineStr">
+        <is>
+          <t>Rent Roll Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="87" t="inlineStr">
+        <is>
+          <t>Property: Hertel Homes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="87" t="inlineStr">
+        <is>
+          <t>As of 08/31/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>Tenant Name</t>
+        </is>
+      </c>
+      <c r="E5" s="87" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="F5" s="87" t="inlineStr">
+        <is>
+          <t>Unit Type</t>
+        </is>
+      </c>
+      <c r="I5" s="87" t="inlineStr">
+        <is>
+          <t>Sq Ft</t>
+        </is>
+      </c>
+      <c r="J5" s="87" t="inlineStr">
+        <is>
+          <t>Market 
+Rent</t>
+        </is>
+      </c>
+      <c r="K5" s="87" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="L5" s="87" t="inlineStr">
+        <is>
+          <t>Vacancy 
+Loss</t>
+        </is>
+      </c>
+      <c r="M5" s="87" t="inlineStr">
+        <is>
+          <t>Misc 
+Charges</t>
+        </is>
+      </c>
+      <c r="O5" s="87" t="inlineStr">
+        <is>
+          <t>Total 
+Charges</t>
+        </is>
+      </c>
+      <c r="P5" s="87" t="inlineStr">
+        <is>
+          <t>Security 
+Deposit</t>
+        </is>
+      </c>
+      <c r="Q5" s="87" t="inlineStr">
+        <is>
+          <t>Increase 
+Amount</t>
+        </is>
+      </c>
+      <c r="R5" s="87" t="inlineStr">
+        <is>
+          <t>Last Rent 
+Increase</t>
+        </is>
+      </c>
+      <c r="S5" s="87" t="inlineStr">
+        <is>
+          <t>Move 
+In</t>
+        </is>
+      </c>
+      <c r="T5" s="87" t="inlineStr">
+        <is>
+          <t>Move 
+Out</t>
+        </is>
+      </c>
+      <c r="U5" s="87" t="inlineStr">
+        <is>
+          <t>Lease 
+End</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="87" t="inlineStr">
+        <is>
+          <t>Hertel Homes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" s="87" t="inlineStr">
+        <is>
+          <t>Echevarria, Amayrani</t>
+        </is>
+      </c>
+      <c r="E7" s="87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I7" s="88" t="n">
+        <v>1340</v>
+      </c>
+      <c r="J7" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K7" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="L7" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="P7" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q7" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="R7" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="S7" s="90" t="n">
+        <v>45219</v>
+      </c>
+      <c r="U7" s="90" t="n">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="87" t="inlineStr">
+        <is>
+          <t>Sanders (BEL), Lasyon</t>
+        </is>
+      </c>
+      <c r="E8" s="87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F8" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I8" s="88" t="n">
+        <v>1340</v>
+      </c>
+      <c r="J8" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K8" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L8" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="89" t="n">
+        <v>35</v>
+      </c>
+      <c r="O8" s="89" t="n">
+        <v>1185</v>
+      </c>
+      <c r="P8" s="89" t="n">
+        <v>400</v>
+      </c>
+      <c r="Q8" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="R8" s="87" t="inlineStr">
+        <is>
+          <t>09/01/25</t>
+        </is>
+      </c>
+      <c r="S8" s="90" t="n">
+        <v>38443</v>
+      </c>
+      <c r="U8" s="90" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" s="87" t="inlineStr">
+        <is>
+          <t>Terry, Daniele</t>
+        </is>
+      </c>
+      <c r="E9" s="87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F9" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I9" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J9" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K9" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L9" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="P9" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q9" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="R9" s="87" t="inlineStr">
+        <is>
+          <t>11/12/25</t>
+        </is>
+      </c>
+      <c r="S9" s="90" t="n">
+        <v>45971</v>
+      </c>
+      <c r="U9" s="90" t="n">
+        <v>46721</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="87" t="inlineStr">
+        <is>
+          <t>Medina, Dylan</t>
+        </is>
+      </c>
+      <c r="E10" s="87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I10" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J10" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K10" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L10" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P10" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q10" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R10" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S10" s="90" t="n">
+        <v>44713</v>
+      </c>
+      <c r="U10" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" s="87" t="inlineStr">
+        <is>
+          <t>Duffy, Denise</t>
+        </is>
+      </c>
+      <c r="E11" s="87" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F11" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I11" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J11" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K11" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L11" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="P11" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="Q11" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R11" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="S11" s="90" t="n">
+        <v>45017</v>
+      </c>
+      <c r="U11" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" s="87" t="inlineStr">
+        <is>
+          <t>Bellamy, Sade</t>
+        </is>
+      </c>
+      <c r="E12" s="87" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F12" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I12" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J12" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K12" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L12" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P12" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q12" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R12" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S12" s="90" t="n">
+        <v>43500</v>
+      </c>
+      <c r="U12" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="87" t="inlineStr">
+        <is>
+          <t>Durham, Dawna</t>
+        </is>
+      </c>
+      <c r="E13" s="87" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I13" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J13" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K13" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L13" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P13" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q13" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R13" s="87" t="inlineStr">
+        <is>
+          <t>03/26/25</t>
+        </is>
+      </c>
+      <c r="S13" s="90" t="n">
+        <v>45748</v>
+      </c>
+      <c r="U13" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" s="87" t="inlineStr">
+        <is>
+          <t>Chaney, Tamea</t>
+        </is>
+      </c>
+      <c r="E14" s="87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F14" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I14" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J14" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K14" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L14" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P14" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q14" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R14" s="87" t="inlineStr">
+        <is>
+          <t>05/01/26</t>
+        </is>
+      </c>
+      <c r="S14" s="90" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U14" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="87" t="inlineStr">
+        <is>
+          <t>Lewis, Trendel</t>
+        </is>
+      </c>
+      <c r="E15" s="87" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F15" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I15" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J15" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K15" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L15" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="O15" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="P15" s="89" t="n">
+        <v>595</v>
+      </c>
+      <c r="Q15" s="89" t="n">
+        <v>225</v>
+      </c>
+      <c r="R15" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="S15" s="90" t="n">
+        <v>41183</v>
+      </c>
+      <c r="U15" s="90" t="n">
+        <v>46660</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" s="87" t="inlineStr">
+        <is>
+          <t>Kuzub (RACB), Marlene</t>
+        </is>
+      </c>
+      <c r="E16" s="87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I16" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J16" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K16" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L16" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="P16" s="89" t="n">
+        <v>595</v>
+      </c>
+      <c r="Q16" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R16" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S16" s="90" t="n">
+        <v>40664</v>
+      </c>
+      <c r="U16" s="90" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="87" t="inlineStr">
+        <is>
+          <t>Gamblin (BFNC), Kizzy</t>
+        </is>
+      </c>
+      <c r="E17" s="87" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F17" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I17" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J17" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K17" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L17" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="O17" s="89" t="n">
+        <v>1025</v>
+      </c>
+      <c r="P17" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q17" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="90" t="n">
+        <v>42156</v>
+      </c>
+      <c r="U17" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="87" t="inlineStr">
+        <is>
+          <t>Caseres, Yadrieliz</t>
+        </is>
+      </c>
+      <c r="E18" s="87" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F18" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I18" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J18" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K18" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L18" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="P18" s="89" t="n">
+        <v>1395</v>
+      </c>
+      <c r="Q18" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" s="87" t="inlineStr">
+        <is>
+          <t>02/01/25</t>
+        </is>
+      </c>
+      <c r="S18" s="90" t="n">
+        <v>44896</v>
+      </c>
+      <c r="U18" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="87" t="inlineStr">
+        <is>
+          <t>Payne (BFNC), Ulysses</t>
+        </is>
+      </c>
+      <c r="E19" s="87" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F19" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I19" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J19" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K19" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L19" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="P19" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="R19" s="87" t="inlineStr">
+        <is>
+          <t>10/06/25</t>
+        </is>
+      </c>
+      <c r="S19" s="90" t="n">
+        <v>45945</v>
+      </c>
+      <c r="U19" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="87" t="inlineStr">
+        <is>
+          <t>Davis, Ebony</t>
+        </is>
+      </c>
+      <c r="E20" s="87" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F20" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I20" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J20" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K20" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L20" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P20" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q20" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R20" s="87" t="inlineStr">
+        <is>
+          <t>01/28/26</t>
+        </is>
+      </c>
+      <c r="S20" s="90" t="n">
+        <v>46053</v>
+      </c>
+      <c r="U20" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="87" t="inlineStr">
+        <is>
+          <t>Barner, Ne'Quan</t>
+        </is>
+      </c>
+      <c r="E21" s="87" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F21" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I21" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J21" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K21" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L21" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P21" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q21" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R21" s="87" t="inlineStr">
+        <is>
+          <t>12/31/25</t>
+        </is>
+      </c>
+      <c r="S21" s="90" t="n">
+        <v>46023</v>
+      </c>
+      <c r="U21" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="87" t="inlineStr">
+        <is>
+          <t>Showard, Brianna</t>
+        </is>
+      </c>
+      <c r="E22" s="87" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F22" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I22" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J22" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K22" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L22" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P22" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R22" s="87" t="inlineStr">
+        <is>
+          <t>02/06/26</t>
+        </is>
+      </c>
+      <c r="S22" s="90" t="n">
+        <v>46037</v>
+      </c>
+      <c r="U22" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E23" s="87" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F23" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I23" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J23" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K23" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L23" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="M23" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" s="87" t="inlineStr">
+        <is>
+          <t>Cash, Najah</t>
+        </is>
+      </c>
+      <c r="E24" s="87" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F24" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I24" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J24" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K24" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L24" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="P24" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q24" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="R24" s="87" t="inlineStr">
+        <is>
+          <t>09/25/25</t>
+        </is>
+      </c>
+      <c r="S24" s="90" t="n">
+        <v>45931</v>
+      </c>
+      <c r="U24" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" s="87" t="inlineStr">
+        <is>
+          <t>Correa (BEL), Carlin</t>
+        </is>
+      </c>
+      <c r="E25" s="87" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F25" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I25" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J25" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K25" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L25" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P25" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="Q25" s="89" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="R25" s="87" t="inlineStr">
+        <is>
+          <t>07/03/25</t>
+        </is>
+      </c>
+      <c r="S25" s="90" t="n">
+        <v>43888</v>
+      </c>
+      <c r="U25" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="87" t="inlineStr">
+        <is>
+          <t>Crawford, Lori</t>
+        </is>
+      </c>
+      <c r="E26" s="87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F26" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I26" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J26" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K26" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L26" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="89" t="n">
+        <v>105</v>
+      </c>
+      <c r="O26" s="89" t="n">
+        <v>1555</v>
+      </c>
+      <c r="P26" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q26" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="R26" s="87" t="inlineStr">
+        <is>
+          <t>09/23/24</t>
+        </is>
+      </c>
+      <c r="S26" s="90" t="n">
+        <v>45565</v>
+      </c>
+      <c r="U26" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="87" t="inlineStr">
+        <is>
+          <t>Coffey, Duane</t>
+        </is>
+      </c>
+      <c r="E27" s="87" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F27" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I27" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J27" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K27" s="89" t="n">
+        <v>800</v>
+      </c>
+      <c r="L27" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="89" t="n">
+        <v>800</v>
+      </c>
+      <c r="P27" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q27" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="R27" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="S27" s="90" t="n">
+        <v>40299</v>
+      </c>
+      <c r="U27" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="87" t="inlineStr">
+        <is>
+          <t>Miller, Richelle</t>
+        </is>
+      </c>
+      <c r="E28" s="87" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F28" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I28" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J28" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K28" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L28" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P28" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="Q28" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R28" s="87" t="inlineStr">
+        <is>
+          <t>03/09/26</t>
+        </is>
+      </c>
+      <c r="S28" s="90" t="n">
+        <v>46106</v>
+      </c>
+      <c r="U28" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="87" t="inlineStr">
+        <is>
+          <t>McDuffie, Adaysha</t>
+        </is>
+      </c>
+      <c r="E29" s="87" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F29" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I29" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J29" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K29" s="89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="L29" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="89" t="n">
+        <v>1600</v>
+      </c>
+      <c r="P29" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="Q29" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R29" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S29" s="90" t="n">
+        <v>45078</v>
+      </c>
+      <c r="U29" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="87" t="inlineStr">
+        <is>
+          <t>Dandridge, Maria</t>
+        </is>
+      </c>
+      <c r="E30" s="87" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F30" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I30" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J30" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K30" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L30" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P30" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q30" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R30" s="87" t="inlineStr">
+        <is>
+          <t>01/21/26</t>
+        </is>
+      </c>
+      <c r="S30" s="90" t="n">
+        <v>46045</v>
+      </c>
+      <c r="U30" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="87" t="inlineStr">
+        <is>
+          <t>Hudson, Tanya</t>
+        </is>
+      </c>
+      <c r="E31" s="87" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F31" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I31" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J31" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K31" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L31" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P31" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q31" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R31" s="87" t="inlineStr">
+        <is>
+          <t>05/08/26</t>
+        </is>
+      </c>
+      <c r="S31" s="90" t="n">
+        <v>46174</v>
+      </c>
+      <c r="U31" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="87" t="inlineStr">
+        <is>
+          <t>Cramer, Mary</t>
+        </is>
+      </c>
+      <c r="E32" s="87" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F32" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I32" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J32" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K32" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L32" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P32" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q32" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R32" s="87" t="inlineStr">
+        <is>
+          <t>02/19/26</t>
+        </is>
+      </c>
+      <c r="S32" s="90" t="n">
+        <v>46096</v>
+      </c>
+      <c r="U32" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="87" t="inlineStr">
+        <is>
+          <t>Dittrich, Ashley</t>
+        </is>
+      </c>
+      <c r="E33" s="87" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F33" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I33" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J33" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K33" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L33" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P33" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="Q33" s="89" t="n">
+        <v>70</v>
+      </c>
+      <c r="R33" s="87" t="inlineStr">
+        <is>
+          <t>12/01/25</t>
+        </is>
+      </c>
+      <c r="S33" s="90" t="n">
+        <v>45258</v>
+      </c>
+      <c r="U33" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="87" t="inlineStr">
+        <is>
+          <t>Pena, Deja</t>
+        </is>
+      </c>
+      <c r="E34" s="87" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F34" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I34" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J34" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K34" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L34" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P34" s="89" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q34" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R34" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S34" s="90" t="n">
+        <v>43763</v>
+      </c>
+      <c r="U34" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="87" t="inlineStr">
+        <is>
+          <t>Berry (BEL), Delores</t>
+        </is>
+      </c>
+      <c r="E35" s="87" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="F35" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I35" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J35" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K35" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L35" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="O35" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="P35" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q35" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="R35" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="S35" s="90" t="n">
+        <v>43419</v>
+      </c>
+      <c r="U35" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E36" s="87" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F36" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I36" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J36" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K36" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L36" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M36" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="87" t="inlineStr">
+        <is>
+          <t>Nemi-Mack (BFNC), Jaiana</t>
+        </is>
+      </c>
+      <c r="E37" s="87" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F37" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I37" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J37" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K37" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L37" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P37" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R37" s="87" t="inlineStr">
+        <is>
+          <t>10/06/25</t>
+        </is>
+      </c>
+      <c r="S37" s="90" t="n">
+        <v>45945</v>
+      </c>
+      <c r="U37" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="87" t="inlineStr">
+        <is>
+          <t>Parker-Hall, Alma</t>
+        </is>
+      </c>
+      <c r="E38" s="87" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F38" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I38" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J38" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K38" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L38" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P38" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R38" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S38" s="90" t="n">
+        <v>43363</v>
+      </c>
+      <c r="U38" s="90" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="87" t="inlineStr">
+        <is>
+          <t>Alexander, Jennell</t>
+        </is>
+      </c>
+      <c r="E39" s="87" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F39" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I39" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J39" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K39" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L39" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="P39" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q39" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="R39" s="87" t="inlineStr">
+        <is>
+          <t>05/01/26</t>
+        </is>
+      </c>
+      <c r="S39" s="90" t="n">
+        <v>43195</v>
+      </c>
+      <c r="U39" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" s="87" t="inlineStr">
+        <is>
+          <t>Colon (BMHA), Jami'lis</t>
+        </is>
+      </c>
+      <c r="E40" s="87" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F40" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I40" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J40" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K40" s="89" t="n">
+        <v>950</v>
+      </c>
+      <c r="L40" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="89" t="n">
+        <v>950</v>
+      </c>
+      <c r="P40" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="R40" s="87" t="inlineStr">
+        <is>
+          <t>09/01/24</t>
+        </is>
+      </c>
+      <c r="S40" s="90" t="n">
+        <v>42614</v>
+      </c>
+      <c r="U40" s="90" t="n">
+        <v>45900</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="87" t="inlineStr">
+        <is>
+          <t>Santiago (RACB), Maria</t>
+        </is>
+      </c>
+      <c r="E41" s="87" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F41" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I41" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J41" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K41" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L41" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O41" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P41" s="89" t="n">
+        <v>405</v>
+      </c>
+      <c r="Q41" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="R41" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="S41" s="90" t="n">
+        <v>38777</v>
+      </c>
+      <c r="U41" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="87" t="inlineStr">
+        <is>
+          <t>Mangier Parra, Luis</t>
+        </is>
+      </c>
+      <c r="E42" s="87" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="F42" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I42" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J42" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K42" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L42" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="P42" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q42" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="R42" s="87" t="inlineStr">
+        <is>
+          <t>02/01/24</t>
+        </is>
+      </c>
+      <c r="S42" s="90" t="n">
+        <v>45328</v>
+      </c>
+      <c r="U42" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="87" t="inlineStr">
+        <is>
+          <t>Kennelly, Brooke</t>
+        </is>
+      </c>
+      <c r="E43" s="87" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="F43" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I43" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J43" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K43" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L43" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P43" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q43" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="R43" s="87" t="inlineStr">
+        <is>
+          <t>06/04/26</t>
+        </is>
+      </c>
+      <c r="S43" s="90" t="n">
+        <v>46193</v>
+      </c>
+      <c r="U43" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="87" t="inlineStr">
+        <is>
+          <t>Brown, Katlyn</t>
+        </is>
+      </c>
+      <c r="E44" s="87" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F44" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I44" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J44" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K44" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L44" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="P44" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="Q44" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="R44" s="87" t="inlineStr">
+        <is>
+          <t>04/13/26</t>
+        </is>
+      </c>
+      <c r="S44" s="90" t="n">
+        <v>46143</v>
+      </c>
+      <c r="U44" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" s="87" t="inlineStr">
+        <is>
+          <t>Lopez (RACB), Chantel</t>
+        </is>
+      </c>
+      <c r="E45" s="87" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F45" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I45" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J45" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K45" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L45" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P45" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q45" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R45" s="87" t="inlineStr">
+        <is>
+          <t>03/16/26</t>
+        </is>
+      </c>
+      <c r="S45" s="90" t="n">
+        <v>46113</v>
+      </c>
+      <c r="U45" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="87" t="inlineStr">
+        <is>
+          <t>Falcon, Alejandra</t>
+        </is>
+      </c>
+      <c r="E46" s="87" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F46" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I46" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J46" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K46" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L46" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P46" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="Q46" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="R46" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="S46" s="90" t="n">
+        <v>45443</v>
+      </c>
+      <c r="U46" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="87" t="inlineStr">
+        <is>
+          <t>Beasley/Solomon, Christine/Dorothy</t>
+        </is>
+      </c>
+      <c r="E47" s="87" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F47" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I47" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J47" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K47" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L47" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="O47" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P47" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="Q47" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R47" s="87" t="inlineStr">
+        <is>
+          <t>09/01/25</t>
+        </is>
+      </c>
+      <c r="S47" s="90" t="n">
+        <v>37987</v>
+      </c>
+      <c r="U47" s="90" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="87" t="inlineStr">
+        <is>
+          <t>Lozada, Jessica</t>
+        </is>
+      </c>
+      <c r="E48" s="87" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F48" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I48" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J48" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K48" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L48" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="P48" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="R48" s="87" t="inlineStr">
+        <is>
+          <t>09/01/25</t>
+        </is>
+      </c>
+      <c r="S48" s="90" t="n">
+        <v>40770</v>
+      </c>
+      <c r="U48" s="90" t="n">
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" s="87" t="inlineStr">
+        <is>
+          <t>Ridgeway, Jayce</t>
+        </is>
+      </c>
+      <c r="E49" s="87" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F49" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I49" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J49" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K49" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L49" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P49" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q49" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R49" s="87" t="inlineStr">
+        <is>
+          <t>04/02/26</t>
+        </is>
+      </c>
+      <c r="S49" s="90" t="n">
+        <v>46127</v>
+      </c>
+      <c r="U49" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="87" t="inlineStr">
+        <is>
+          <t>Jefferson (BEL), Kenneth</t>
+        </is>
+      </c>
+      <c r="E50" s="87" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F50" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I50" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J50" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K50" s="89" t="n">
+        <v>1198</v>
+      </c>
+      <c r="L50" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="89" t="n">
+        <v>1198</v>
+      </c>
+      <c r="P50" s="89" t="n">
+        <v>1185</v>
+      </c>
+      <c r="Q50" s="89" t="n">
+        <v>13</v>
+      </c>
+      <c r="R50" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="S50" s="90" t="n">
+        <v>45331</v>
+      </c>
+      <c r="U50" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="87" t="inlineStr">
+        <is>
+          <t>Bowens, Dana</t>
+        </is>
+      </c>
+      <c r="E51" s="87" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="F51" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I51" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J51" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K51" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="P51" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q51" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R51" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="S51" s="90" t="n">
+        <v>42551</v>
+      </c>
+      <c r="U51" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" s="87" t="inlineStr">
+        <is>
+          <t>Thurman, Tyler</t>
+        </is>
+      </c>
+      <c r="E52" s="87" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F52" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I52" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J52" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K52" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L52" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P52" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q52" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R52" s="87" t="inlineStr">
+        <is>
+          <t>03/24/26</t>
+        </is>
+      </c>
+      <c r="S52" s="90" t="n">
+        <v>46111</v>
+      </c>
+      <c r="U52" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="87" t="inlineStr">
+        <is>
+          <t>Hampton, Kayla</t>
+        </is>
+      </c>
+      <c r="E53" s="87" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F53" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I53" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J53" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K53" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="L53" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="P53" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="R53" s="87" t="inlineStr">
+        <is>
+          <t>03/12/26</t>
+        </is>
+      </c>
+      <c r="S53" s="90" t="n">
+        <v>46113</v>
+      </c>
+      <c r="U53" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" s="87" t="inlineStr">
+        <is>
+          <t>Febles, Miguel</t>
+        </is>
+      </c>
+      <c r="E54" s="87" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F54" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I54" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J54" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K54" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="L54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="P54" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q54" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R54" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="S54" s="90" t="n">
+        <v>45565</v>
+      </c>
+      <c r="U54" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="87" t="inlineStr">
+        <is>
+          <t>Clarke, Brandon</t>
+        </is>
+      </c>
+      <c r="E55" s="87" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F55" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I55" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J55" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K55" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L55" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="O55" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="P55" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q55" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R55" s="87" t="inlineStr">
+        <is>
+          <t>02/06/26</t>
+        </is>
+      </c>
+      <c r="S55" s="90" t="n">
+        <v>46051</v>
+      </c>
+      <c r="U55" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="87" t="inlineStr">
+        <is>
+          <t>Cardoza, Patricia</t>
+        </is>
+      </c>
+      <c r="E56" s="87" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F56" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I56" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J56" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K56" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P56" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q56" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R56" s="87" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
+      <c r="S56" s="90" t="n">
+        <v>46204</v>
+      </c>
+      <c r="U56" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="87" t="inlineStr">
+        <is>
+          <t>Services Inc., Transitional</t>
+        </is>
+      </c>
+      <c r="E57" s="87" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F57" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I57" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J57" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K57" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="P57" s="89" t="n">
+        <v>650</v>
+      </c>
+      <c r="Q57" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="R57" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="S57" s="90" t="n">
+        <v>41091</v>
+      </c>
+      <c r="U57" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E58" s="87" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F58" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I58" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J58" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K58" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L58" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="87" t="inlineStr">
+        <is>
+          <t>Alvarez Pinero, Kathy</t>
+        </is>
+      </c>
+      <c r="E59" s="87" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F59" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I59" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J59" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K59" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L59" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P59" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q59" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R59" s="87" t="inlineStr">
+        <is>
+          <t>01/20/26</t>
+        </is>
+      </c>
+      <c r="S59" s="90" t="n">
+        <v>46057</v>
+      </c>
+      <c r="U59" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="87" t="inlineStr">
+        <is>
+          <t>Jaycox, Alfred</t>
+        </is>
+      </c>
+      <c r="E60" s="87" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F60" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I60" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J60" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K60" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L60" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O60" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="P60" s="89" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q60" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R60" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S60" s="90" t="n">
+        <v>44215</v>
+      </c>
+      <c r="U60" s="90" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="87" t="inlineStr">
+        <is>
+          <t>Brown, John</t>
+        </is>
+      </c>
+      <c r="E61" s="87" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F61" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I61" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J61" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K61" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="P61" s="89" t="n">
+        <v>405</v>
+      </c>
+      <c r="Q61" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="R61" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="S61" s="90" t="n">
+        <v>38764</v>
+      </c>
+      <c r="U61" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="87" t="inlineStr">
+        <is>
+          <t>Arroyo, Feridinand</t>
+        </is>
+      </c>
+      <c r="E62" s="87" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F62" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I62" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J62" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K62" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L62" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O62" s="89" t="n">
+        <v>1245</v>
+      </c>
+      <c r="P62" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="Q62" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R62" s="87" t="inlineStr">
+        <is>
+          <t>02/19/26</t>
+        </is>
+      </c>
+      <c r="S62" s="90" t="n">
+        <v>46082</v>
+      </c>
+      <c r="U62" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="87" t="inlineStr">
+        <is>
+          <t>Woodfork, Alex</t>
+        </is>
+      </c>
+      <c r="E63" s="87" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F63" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I63" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J63" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K63" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L63" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P63" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q63" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R63" s="87" t="inlineStr">
+        <is>
+          <t>08/05/25</t>
+        </is>
+      </c>
+      <c r="S63" s="90" t="n">
+        <v>45898</v>
+      </c>
+      <c r="U63" s="90" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" s="87" t="inlineStr">
+        <is>
+          <t>Thomas, Marie Magdala</t>
+        </is>
+      </c>
+      <c r="E64" s="87" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F64" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I64" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J64" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K64" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L64" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P64" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q64" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R64" s="87" t="inlineStr">
+        <is>
+          <t>04/04/25</t>
+        </is>
+      </c>
+      <c r="S64" s="90" t="n">
+        <v>45754</v>
+      </c>
+      <c r="U64" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="87" t="inlineStr">
+        <is>
+          <t>Smith, Carla</t>
+        </is>
+      </c>
+      <c r="E65" s="87" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F65" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I65" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J65" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K65" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L65" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="P65" s="89" t="n">
+        <v>710</v>
+      </c>
+      <c r="Q65" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="R65" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="S65" s="90" t="n">
+        <v>41487</v>
+      </c>
+      <c r="U65" s="90" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="87" t="inlineStr">
+        <is>
+          <t>Herby (BMHA), Leah</t>
+        </is>
+      </c>
+      <c r="E66" s="87" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F66" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I66" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J66" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K66" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="L66" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="P66" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="R66" s="87" t="inlineStr">
+        <is>
+          <t>04/15/26</t>
+        </is>
+      </c>
+      <c r="S66" s="90" t="n">
+        <v>46143</v>
+      </c>
+      <c r="U66" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="87" t="inlineStr">
+        <is>
+          <t>Perez (RACB), Carmen</t>
+        </is>
+      </c>
+      <c r="E67" s="87" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="F67" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I67" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J67" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K67" s="89" t="n">
+        <v>1250</v>
+      </c>
+      <c r="L67" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O67" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P67" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q67" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="R67" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="S67" s="90" t="n">
+        <v>40878</v>
+      </c>
+      <c r="U67" s="90" t="n">
+        <v>46721</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E68" s="87" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F68" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I68" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J68" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K68" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L68" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M68" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="87" t="inlineStr">
+        <is>
+          <t>Leon Rodriguez (RACB), Jose Luis</t>
+        </is>
+      </c>
+      <c r="E69" s="87" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F69" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I69" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J69" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K69" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L69" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P69" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="R69" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S69" s="90" t="n">
+        <v>42829</v>
+      </c>
+      <c r="U69" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="87" t="inlineStr">
+        <is>
+          <t>Myers, Ty</t>
+        </is>
+      </c>
+      <c r="E70" s="87" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F70" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I70" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J70" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K70" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L70" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P70" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q70" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R70" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="S70" s="90" t="n">
+        <v>40589</v>
+      </c>
+      <c r="U70" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" s="87" t="inlineStr">
+        <is>
+          <t>Carson (BEL), Joyce</t>
+        </is>
+      </c>
+      <c r="E71" s="87" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F71" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I71" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J71" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K71" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L71" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O71" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P71" s="89" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q71" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R71" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S71" s="90" t="n">
+        <v>39731</v>
+      </c>
+      <c r="U71" s="90" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" s="87" t="inlineStr">
+        <is>
+          <t>Chesson (BEL), Amuniquee</t>
+        </is>
+      </c>
+      <c r="E72" s="87" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F72" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I72" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J72" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K72" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L72" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P72" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q72" s="89" t="n">
+        <v>61</v>
+      </c>
+      <c r="R72" s="87" t="inlineStr">
+        <is>
+          <t>11/01/24</t>
+        </is>
+      </c>
+      <c r="S72" s="90" t="n">
+        <v>45245</v>
+      </c>
+      <c r="U72" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" s="87" t="inlineStr">
+        <is>
+          <t>Roland, Mildred</t>
+        </is>
+      </c>
+      <c r="E73" s="87" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F73" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I73" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J73" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K73" s="89" t="n">
+        <v>900</v>
+      </c>
+      <c r="L73" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="89" t="n">
+        <v>900</v>
+      </c>
+      <c r="P73" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="89" t="n">
+        <v>5</v>
+      </c>
+      <c r="R73" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S73" s="90" t="n">
+        <v>42307</v>
+      </c>
+      <c r="U73" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" s="87" t="inlineStr">
+        <is>
+          <t>Lewis, Earlisa</t>
+        </is>
+      </c>
+      <c r="E74" s="87" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F74" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I74" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J74" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K74" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="L74" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="P74" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R74" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="S74" s="90" t="n">
+        <v>45139</v>
+      </c>
+      <c r="U74" s="90" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E75" s="87" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F75" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I75" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J75" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K75" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L75" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M75" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" s="87" t="inlineStr">
+        <is>
+          <t>Ball, Ruby</t>
+        </is>
+      </c>
+      <c r="E76" s="87" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F76" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I76" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J76" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K76" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="L76" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="O76" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="P76" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q76" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R76" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="S76" s="90" t="n">
+        <v>44372</v>
+      </c>
+      <c r="U76" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" s="87" t="inlineStr">
+        <is>
+          <t>Williams (BEL), Earl</t>
+        </is>
+      </c>
+      <c r="E77" s="87" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F77" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I77" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J77" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K77" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L77" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P77" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q77" s="89" t="n">
+        <v>300</v>
+      </c>
+      <c r="R77" s="87" t="inlineStr">
+        <is>
+          <t>01/01/26</t>
+        </is>
+      </c>
+      <c r="S77" s="90" t="n">
+        <v>43332</v>
+      </c>
+      <c r="U77" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" s="87" t="inlineStr">
+        <is>
+          <t>Services, TSI, Transitional</t>
+        </is>
+      </c>
+      <c r="E78" s="87" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F78" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I78" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J78" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K78" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="L78" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="89" t="n">
+        <v>1425</v>
+      </c>
+      <c r="P78" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q78" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R78" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="S78" s="90" t="n">
+        <v>45467</v>
+      </c>
+      <c r="U78" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" s="87" t="inlineStr">
+        <is>
+          <t>Matos (RACB), Alida</t>
+        </is>
+      </c>
+      <c r="E79" s="87" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F79" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I79" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J79" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K79" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L79" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="P79" s="89" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q79" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="R79" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S79" s="90" t="n">
+        <v>37986</v>
+      </c>
+      <c r="U79" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" s="87" t="inlineStr">
+        <is>
+          <t>Robinson, Felicia</t>
+        </is>
+      </c>
+      <c r="E80" s="87" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F80" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I80" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J80" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K80" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L80" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P80" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q80" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R80" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="S80" s="90" t="n">
+        <v>43347</v>
+      </c>
+      <c r="U80" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="87" t="inlineStr">
+        <is>
+          <t>Rodriguez, Juan</t>
+        </is>
+      </c>
+      <c r="E81" s="87" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F81" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I81" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J81" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K81" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L81" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P81" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q81" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R81" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="S81" s="90" t="n">
+        <v>45547</v>
+      </c>
+      <c r="U81" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" s="87" t="inlineStr">
+        <is>
+          <t>Rodriguez (BMHA), Betsy</t>
+        </is>
+      </c>
+      <c r="E82" s="87" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F82" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I82" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J82" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K82" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L82" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P82" s="89" t="n">
+        <v>500</v>
+      </c>
+      <c r="Q82" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R82" s="87" t="inlineStr">
+        <is>
+          <t>02/01/26</t>
+        </is>
+      </c>
+      <c r="S82" s="90" t="n">
+        <v>39783</v>
+      </c>
+      <c r="U82" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" s="87" t="inlineStr">
+        <is>
+          <t>Clemons, Shandy</t>
+        </is>
+      </c>
+      <c r="E83" s="87" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F83" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I83" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J83" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K83" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L83" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P83" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q83" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="R83" s="87" t="inlineStr">
+        <is>
+          <t>05/14/26</t>
+        </is>
+      </c>
+      <c r="S83" s="90" t="n">
+        <v>46188</v>
+      </c>
+      <c r="U83" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" s="87" t="inlineStr">
+        <is>
+          <t>Green, Taylor</t>
+        </is>
+      </c>
+      <c r="E84" s="87" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="F84" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I84" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J84" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K84" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L84" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P84" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R84" s="87" t="inlineStr">
+        <is>
+          <t>11/05/25</t>
+        </is>
+      </c>
+      <c r="S84" s="90" t="n">
+        <v>46006</v>
+      </c>
+      <c r="U84" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" s="87" t="inlineStr">
+        <is>
+          <t>Walker (RACB), Teniel</t>
+        </is>
+      </c>
+      <c r="E85" s="87" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F85" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I85" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J85" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K85" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L85" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P85" s="89" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q85" s="89" t="n">
+        <v>125</v>
+      </c>
+      <c r="R85" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S85" s="90" t="n">
+        <v>43556</v>
+      </c>
+      <c r="U85" s="90" t="n">
+        <v>46142</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" s="87" t="inlineStr">
+        <is>
+          <t>Whittle, Wanda</t>
+        </is>
+      </c>
+      <c r="E86" s="87" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F86" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I86" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J86" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K86" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L86" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P86" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="R86" s="87" t="inlineStr">
+        <is>
+          <t>11/01/24</t>
+        </is>
+      </c>
+      <c r="S86" s="90" t="n">
+        <v>42328</v>
+      </c>
+      <c r="U86" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" s="87" t="inlineStr">
+        <is>
+          <t>Anderson, Eric</t>
+        </is>
+      </c>
+      <c r="E87" s="87" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="F87" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I87" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J87" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K87" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L87" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P87" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q87" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R87" s="87" t="inlineStr">
+        <is>
+          <t>04/14/25</t>
+        </is>
+      </c>
+      <c r="S87" s="90" t="n">
+        <v>45762</v>
+      </c>
+      <c r="U87" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" s="87" t="inlineStr">
+        <is>
+          <t>Sosa-Hearn, Griselida</t>
+        </is>
+      </c>
+      <c r="E88" s="87" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="F88" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I88" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J88" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K88" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L88" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O88" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="P88" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q88" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R88" s="87" t="inlineStr">
+        <is>
+          <t>02/19/26</t>
+        </is>
+      </c>
+      <c r="S88" s="90" t="n">
+        <v>46096</v>
+      </c>
+      <c r="U88" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" s="87" t="inlineStr">
+        <is>
+          <t>Wortman, Patrick</t>
+        </is>
+      </c>
+      <c r="E89" s="87" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F89" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I89" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J89" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K89" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L89" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P89" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="Q89" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R89" s="87" t="inlineStr">
+        <is>
+          <t>08/05/25</t>
+        </is>
+      </c>
+      <c r="S89" s="90" t="n">
+        <v>45884</v>
+      </c>
+      <c r="U89" s="90" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" s="87" t="inlineStr">
+        <is>
+          <t>Turner, William</t>
+        </is>
+      </c>
+      <c r="E90" s="87" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F90" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I90" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J90" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K90" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L90" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="89" t="n">
+        <v>200</v>
+      </c>
+      <c r="O90" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P90" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="Q90" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R90" s="87" t="inlineStr">
+        <is>
+          <t>10/27/23</t>
+        </is>
+      </c>
+      <c r="S90" s="90" t="n">
+        <v>45229</v>
+      </c>
+      <c r="U90" s="90" t="n">
+        <v>45596</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" s="87" t="inlineStr">
+        <is>
+          <t>Williams, Erik</t>
+        </is>
+      </c>
+      <c r="E91" s="87" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="F91" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I91" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J91" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K91" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L91" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P91" s="89" t="n">
+        <v>650</v>
+      </c>
+      <c r="Q91" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R91" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="S91" s="90" t="n">
+        <v>43539</v>
+      </c>
+      <c r="U91" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" s="87" t="inlineStr">
+        <is>
+          <t>Brown, Marland</t>
+        </is>
+      </c>
+      <c r="E92" s="87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F92" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I92" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J92" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K92" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="L92" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="P92" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="Q92" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="R92" s="87" t="inlineStr">
+        <is>
+          <t>09/16/25</t>
+        </is>
+      </c>
+      <c r="S92" s="90" t="n">
+        <v>45931</v>
+      </c>
+      <c r="U92" s="90" t="n">
+        <v>46660</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" s="87" t="inlineStr">
+        <is>
+          <t>Harper, Sheontra</t>
+        </is>
+      </c>
+      <c r="E93" s="87" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F93" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I93" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J93" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K93" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L93" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P93" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q93" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R93" s="87" t="inlineStr">
+        <is>
+          <t>02/26/26</t>
+        </is>
+      </c>
+      <c r="S93" s="90" t="n">
+        <v>46081</v>
+      </c>
+      <c r="U93" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" s="87" t="inlineStr">
+        <is>
+          <t>Walker, Jeanette</t>
+        </is>
+      </c>
+      <c r="E94" s="87" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F94" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I94" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J94" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K94" s="89" t="n">
+        <v>995</v>
+      </c>
+      <c r="L94" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="89" t="n">
+        <v>995</v>
+      </c>
+      <c r="P94" s="89" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="Q94" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="R94" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="S94" s="90" t="n">
+        <v>42984</v>
+      </c>
+      <c r="U94" s="90" t="n">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" s="87" t="inlineStr">
+        <is>
+          <t>elmore, clintonia</t>
+        </is>
+      </c>
+      <c r="E95" s="87" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="F95" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I95" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J95" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K95" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L95" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P95" s="89" t="n">
+        <v>1051</v>
+      </c>
+      <c r="Q95" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R95" s="87" t="inlineStr">
+        <is>
+          <t>11/01/24</t>
+        </is>
+      </c>
+      <c r="S95" s="90" t="n">
+        <v>44270</v>
+      </c>
+      <c r="U95" s="90" t="n">
+        <v>45961</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" s="87" t="inlineStr">
+        <is>
+          <t>Lin, Henry</t>
+        </is>
+      </c>
+      <c r="E96" s="87" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F96" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I96" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J96" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K96" s="89" t="n">
+        <v>1145</v>
+      </c>
+      <c r="L96" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="89" t="n">
+        <v>1145</v>
+      </c>
+      <c r="P96" s="89" t="n">
+        <v>1145</v>
+      </c>
+      <c r="Q96" s="89" t="n">
+        <v>1145</v>
+      </c>
+      <c r="R96" s="87" t="inlineStr">
+        <is>
+          <t>06/17/25</t>
+        </is>
+      </c>
+      <c r="S96" s="90" t="n">
+        <v>45831</v>
+      </c>
+      <c r="U96" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="C97" s="87" t="inlineStr">
+        <is>
+          <t>Neasman, Tionisha</t>
+        </is>
+      </c>
+      <c r="E97" s="87" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="F97" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I97" s="88" t="n">
+        <v>1541</v>
+      </c>
+      <c r="J97" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K97" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L97" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P97" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q97" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R97" s="87" t="inlineStr">
+        <is>
+          <t>12/28/23</t>
+        </is>
+      </c>
+      <c r="S97" s="90" t="n">
+        <v>45267</v>
+      </c>
+      <c r="U97" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E98" s="87" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F98" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I98" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J98" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K98" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L98" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="M98" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P98" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" s="87" t="inlineStr">
+        <is>
+          <t>Hussein, Mohamud</t>
+        </is>
+      </c>
+      <c r="E99" s="87" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="F99" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I99" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J99" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K99" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L99" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P99" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q99" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R99" s="87" t="inlineStr">
+        <is>
+          <t>01/09/26</t>
+        </is>
+      </c>
+      <c r="S99" s="90" t="n">
+        <v>46038</v>
+      </c>
+      <c r="U99" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" s="87" t="inlineStr">
+        <is>
+          <t>Jenifer, Poshine</t>
+        </is>
+      </c>
+      <c r="E100" s="87" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F100" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I100" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J100" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K100" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L100" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P100" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q100" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R100" s="87" t="inlineStr">
+        <is>
+          <t>02/13/25</t>
+        </is>
+      </c>
+      <c r="S100" s="90" t="n">
+        <v>45702</v>
+      </c>
+      <c r="U100" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="C101" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E101" s="87" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F101" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I101" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J101" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K101" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L101" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M101" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" s="87" t="inlineStr">
+        <is>
+          <t>Smith (BMHA), Jacqualyn</t>
+        </is>
+      </c>
+      <c r="E102" s="87" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="F102" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I102" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J102" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K102" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L102" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="P102" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R102" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S102" s="90" t="n">
+        <v>42783</v>
+      </c>
+      <c r="U102" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" s="87" t="inlineStr">
+        <is>
+          <t>Coleman, Joseph</t>
+        </is>
+      </c>
+      <c r="E103" s="87" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="F103" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I103" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J103" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K103" s="89" t="n">
+        <v>825</v>
+      </c>
+      <c r="L103" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="89" t="n">
+        <v>825</v>
+      </c>
+      <c r="P103" s="89" t="n">
+        <v>595</v>
+      </c>
+      <c r="Q103" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R103" s="87" t="inlineStr">
+        <is>
+          <t>01/01/25</t>
+        </is>
+      </c>
+      <c r="S103" s="90" t="n">
+        <v>43433</v>
+      </c>
+      <c r="U103" s="90" t="n">
+        <v>46022</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="C104" s="87" t="inlineStr">
+        <is>
+          <t>Bennett, Dezarai</t>
+        </is>
+      </c>
+      <c r="E104" s="87" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F104" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I104" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J104" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K104" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L104" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P104" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q104" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R104" s="87" t="inlineStr">
+        <is>
+          <t>10/25/24</t>
+        </is>
+      </c>
+      <c r="S104" s="90" t="n">
+        <v>45593</v>
+      </c>
+      <c r="U104" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="C105" s="87" t="inlineStr">
+        <is>
+          <t>Harper, Robert</t>
+        </is>
+      </c>
+      <c r="E105" s="87" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="F105" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I105" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J105" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K105" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L105" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="P105" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q105" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R105" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="S105" s="90" t="n">
+        <v>41974</v>
+      </c>
+      <c r="U105" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="C106" s="87" t="inlineStr">
+        <is>
+          <t>Spencer, Gerry</t>
+        </is>
+      </c>
+      <c r="E106" s="87" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F106" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I106" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J106" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K106" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="L106" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="P106" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q106" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R106" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="S106" s="90" t="n">
+        <v>44769</v>
+      </c>
+      <c r="U106" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="C107" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E107" s="87" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F107" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I107" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J107" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K107" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L107" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M107" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="C108" s="87" t="inlineStr">
+        <is>
+          <t>Perez (RACB), Estralita</t>
+        </is>
+      </c>
+      <c r="E108" s="87" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F108" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I108" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J108" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K108" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="L108" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="89" t="n">
+        <v>1225</v>
+      </c>
+      <c r="P108" s="89" t="n">
+        <v>320</v>
+      </c>
+      <c r="Q108" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R108" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S108" s="90" t="n">
+        <v>36831</v>
+      </c>
+      <c r="U108" s="90" t="n">
+        <v>46538</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="C109" s="87" t="inlineStr">
+        <is>
+          <t>Santiago (RACB), Grace</t>
+        </is>
+      </c>
+      <c r="E109" s="87" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="F109" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I109" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J109" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K109" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L109" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="P109" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R109" s="87" t="inlineStr">
+        <is>
+          <t>05/01/24</t>
+        </is>
+      </c>
+      <c r="S109" s="90" t="n">
+        <v>43192</v>
+      </c>
+      <c r="U109" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="C110" s="87" t="inlineStr">
+        <is>
+          <t>Sanchez, Melissa</t>
+        </is>
+      </c>
+      <c r="E110" s="87" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F110" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I110" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J110" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K110" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="L110" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="P110" s="89" t="n">
+        <v>925</v>
+      </c>
+      <c r="Q110" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R110" s="87" t="inlineStr">
+        <is>
+          <t>02/01/26</t>
+        </is>
+      </c>
+      <c r="S110" s="90" t="n">
+        <v>44216</v>
+      </c>
+      <c r="U110" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="C111" s="87" t="inlineStr">
+        <is>
+          <t>Fair, Babette</t>
+        </is>
+      </c>
+      <c r="E111" s="87" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F111" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I111" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J111" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K111" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L111" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="89" t="n">
+        <v>1095</v>
+      </c>
+      <c r="P111" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q111" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="R111" s="87" t="inlineStr">
+        <is>
+          <t>08/01/25</t>
+        </is>
+      </c>
+      <c r="S111" s="90" t="n">
+        <v>40756</v>
+      </c>
+      <c r="U111" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="C112" s="87" t="inlineStr">
+        <is>
+          <t>Harris (BEL), Willette</t>
+        </is>
+      </c>
+      <c r="E112" s="87" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="F112" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I112" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J112" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="K112" s="89" t="n">
+        <v>1209</v>
+      </c>
+      <c r="L112" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="89" t="n">
+        <v>1209</v>
+      </c>
+      <c r="P112" s="89" t="n">
+        <v>1209</v>
+      </c>
+      <c r="Q112" s="89" t="n">
+        <v>1209</v>
+      </c>
+      <c r="R112" s="87" t="inlineStr">
+        <is>
+          <t>10/29/25</t>
+        </is>
+      </c>
+      <c r="S112" s="90" t="n">
+        <v>45962</v>
+      </c>
+      <c r="U112" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="C113" s="87" t="inlineStr">
+        <is>
+          <t>Colon (BEL), Linet</t>
+        </is>
+      </c>
+      <c r="E113" s="87" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F113" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I113" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J113" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K113" s="89" t="n">
+        <v>1209</v>
+      </c>
+      <c r="L113" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="89" t="n">
+        <v>1209</v>
+      </c>
+      <c r="P113" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" s="89" t="n">
+        <v>1209</v>
+      </c>
+      <c r="R113" s="87" t="inlineStr">
+        <is>
+          <t>06/20/25</t>
+        </is>
+      </c>
+      <c r="S113" s="90" t="n">
+        <v>45839</v>
+      </c>
+      <c r="U113" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="C114" s="87" t="inlineStr">
+        <is>
+          <t>Bernard (RACB), Ana</t>
+        </is>
+      </c>
+      <c r="E114" s="87" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="F114" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I114" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J114" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K114" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L114" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="89" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P114" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" s="89" t="n">
+        <v>375</v>
+      </c>
+      <c r="R114" s="87" t="inlineStr">
+        <is>
+          <t>04/01/24</t>
+        </is>
+      </c>
+      <c r="S114" s="90" t="n">
+        <v>42594</v>
+      </c>
+      <c r="U114" s="90" t="n">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="C115" s="87" t="inlineStr">
+        <is>
+          <t>Cardona, Tavializ</t>
+        </is>
+      </c>
+      <c r="E115" s="87" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F115" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I115" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J115" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K115" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L115" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="P115" s="89" t="n">
+        <v>675</v>
+      </c>
+      <c r="Q115" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R115" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="S115" s="90" t="n">
+        <v>42795</v>
+      </c>
+      <c r="U115" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="C116" s="87" t="inlineStr">
+        <is>
+          <t>Carrion (EC), Rosemarie</t>
+        </is>
+      </c>
+      <c r="E116" s="87" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F116" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I116" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J116" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K116" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L116" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O116" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="P116" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R116" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="S116" s="90" t="n">
+        <v>43070</v>
+      </c>
+      <c r="U116" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="C117" s="87" t="inlineStr">
+        <is>
+          <t>Rembert, Kamren</t>
+        </is>
+      </c>
+      <c r="E117" s="87" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="F117" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I117" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J117" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K117" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L117" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O117" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P117" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R117" s="87" t="inlineStr">
+        <is>
+          <t>12/22/25</t>
+        </is>
+      </c>
+      <c r="S117" s="90" t="n">
+        <v>46023</v>
+      </c>
+      <c r="U117" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="C118" s="87" t="inlineStr">
+        <is>
+          <t>Arroyo, Alexander</t>
+        </is>
+      </c>
+      <c r="E118" s="87" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F118" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I118" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J118" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K118" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L118" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O118" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P118" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q118" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R118" s="87" t="inlineStr">
+        <is>
+          <t>10/01/25</t>
+        </is>
+      </c>
+      <c r="S118" s="90" t="n">
+        <v>43011</v>
+      </c>
+      <c r="U118" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="C119" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E119" s="87" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="F119" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I119" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J119" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K119" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L119" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="M119" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="C120" s="87" t="inlineStr">
+        <is>
+          <t>Bishop (BMHA), Candice</t>
+        </is>
+      </c>
+      <c r="E120" s="87" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F120" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I120" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J120" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K120" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L120" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O120" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P120" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R120" s="87" t="inlineStr">
+        <is>
+          <t>02/20/26</t>
+        </is>
+      </c>
+      <c r="S120" s="90" t="n">
+        <v>46082</v>
+      </c>
+      <c r="U120" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="C121" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E121" s="87" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="F121" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I121" s="88" t="n">
+        <v>1141</v>
+      </c>
+      <c r="J121" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K121" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L121" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="M121" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="C122" s="87" t="inlineStr">
+        <is>
+          <t>Wilmet (BEL), Joann</t>
+        </is>
+      </c>
+      <c r="E122" s="87" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F122" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I122" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J122" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K122" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L122" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P122" s="89" t="n">
+        <v>525</v>
+      </c>
+      <c r="Q122" s="89" t="n">
+        <v>-1150</v>
+      </c>
+      <c r="R122" s="87" t="inlineStr">
+        <is>
+          <t>07/02/25</t>
+        </is>
+      </c>
+      <c r="S122" s="90" t="n">
+        <v>41153</v>
+      </c>
+      <c r="U122" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="C123" s="87" t="inlineStr">
+        <is>
+          <t>Reed, Siann</t>
+        </is>
+      </c>
+      <c r="E123" s="87" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="F123" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I123" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J123" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="K123" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L123" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P123" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="Q123" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="R123" s="87" t="inlineStr">
+        <is>
+          <t>07/14/25</t>
+        </is>
+      </c>
+      <c r="S123" s="90" t="n">
+        <v>45853</v>
+      </c>
+      <c r="U123" s="90" t="n">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="C124" s="87" t="inlineStr">
+        <is>
+          <t>Henderson (BFNC), Marilyn</t>
+        </is>
+      </c>
+      <c r="E124" s="87" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="F124" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I124" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J124" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K124" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L124" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P124" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R124" s="87" t="inlineStr">
+        <is>
+          <t>09/30/25</t>
+        </is>
+      </c>
+      <c r="S124" s="90" t="n">
+        <v>45923</v>
+      </c>
+      <c r="U124" s="90" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="C125" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E125" s="87" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F125" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I125" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J125" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K125" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="L125" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="M125" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="C126" s="87" t="inlineStr">
+        <is>
+          <t>Smith, Aaron</t>
+        </is>
+      </c>
+      <c r="E126" s="87" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F126" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I126" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J126" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K126" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L126" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P126" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="R126" s="87" t="inlineStr">
+        <is>
+          <t>07/02/26</t>
+        </is>
+      </c>
+      <c r="S126" s="90" t="n">
+        <v>46206</v>
+      </c>
+      <c r="U126" s="90" t="n">
+        <v>46599</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="C127" s="87" t="inlineStr">
+        <is>
+          <t>Harden, Andrea</t>
+        </is>
+      </c>
+      <c r="E127" s="87" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="F127" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I127" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J127" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K127" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L127" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O127" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P127" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="Q127" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R127" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S127" s="90" t="n">
+        <v>45031</v>
+      </c>
+      <c r="U127" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="C128" s="87" t="inlineStr">
+        <is>
+          <t>TSI, Transitional Services</t>
+        </is>
+      </c>
+      <c r="E128" s="87" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="F128" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I128" s="88" t="n">
+        <v>1141</v>
+      </c>
+      <c r="J128" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K128" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L128" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P128" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q128" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="R128" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="S128" s="90" t="n">
+        <v>45383</v>
+      </c>
+      <c r="U128" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" s="87" t="inlineStr">
+        <is>
+          <t>Ubinas, Mariah</t>
+        </is>
+      </c>
+      <c r="E129" s="87" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F129" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I129" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J129" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K129" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L129" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="P129" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q129" s="89" t="n">
+        <v>80</v>
+      </c>
+      <c r="R129" s="87" t="inlineStr">
+        <is>
+          <t>09/01/25</t>
+        </is>
+      </c>
+      <c r="S129" s="90" t="n">
+        <v>44062</v>
+      </c>
+      <c r="U129" s="90" t="n">
+        <v>46630</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="C130" s="87" t="inlineStr">
+        <is>
+          <t>Brown (BFNC), Derron</t>
+        </is>
+      </c>
+      <c r="E130" s="87" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="F130" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I130" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J130" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K130" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L130" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P130" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="Q130" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R130" s="87" t="inlineStr">
+        <is>
+          <t>10/22/25</t>
+        </is>
+      </c>
+      <c r="S130" s="90" t="n">
+        <v>45961</v>
+      </c>
+      <c r="U130" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="C131" s="87" t="inlineStr">
+        <is>
+          <t>Chance (Bel), Jordynne</t>
+        </is>
+      </c>
+      <c r="E131" s="87" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F131" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I131" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J131" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="K131" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L131" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="P131" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q131" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="R131" s="87" t="inlineStr">
+        <is>
+          <t>06/25/25</t>
+        </is>
+      </c>
+      <c r="S131" s="90" t="n">
+        <v>45839</v>
+      </c>
+      <c r="U131" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="C132" s="87" t="inlineStr">
+        <is>
+          <t>Alomar Colon (BMHA), Javier</t>
+        </is>
+      </c>
+      <c r="E132" s="87" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="F132" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I132" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J132" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K132" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L132" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="P132" s="89" t="n">
+        <v>485</v>
+      </c>
+      <c r="Q132" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R132" s="87" t="inlineStr">
+        <is>
+          <t>02/01/26</t>
+        </is>
+      </c>
+      <c r="S132" s="90" t="n">
+        <v>42754</v>
+      </c>
+      <c r="U132" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="C133" s="87" t="inlineStr">
+        <is>
+          <t>Golden (RACB), India</t>
+        </is>
+      </c>
+      <c r="E133" s="87" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="F133" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I133" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J133" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K133" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="L133" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="89" t="n">
+        <v>1175</v>
+      </c>
+      <c r="P133" s="89" t="n">
+        <v>685</v>
+      </c>
+      <c r="Q133" s="89" t="n">
+        <v>150</v>
+      </c>
+      <c r="R133" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="S133" s="90" t="n">
+        <v>41730</v>
+      </c>
+      <c r="U133" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="C134" s="87" t="inlineStr">
+        <is>
+          <t>Daza, Brenda</t>
+        </is>
+      </c>
+      <c r="E134" s="87" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="F134" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I134" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J134" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K134" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="L134" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" s="89" t="n">
+        <v>1295</v>
+      </c>
+      <c r="P134" s="89" t="n">
+        <v>900</v>
+      </c>
+      <c r="Q134" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="R134" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S134" s="90" t="n">
+        <v>44028</v>
+      </c>
+      <c r="U134" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="C135" s="87" t="inlineStr">
+        <is>
+          <t>Diggs, Daeaira</t>
+        </is>
+      </c>
+      <c r="E135" s="87" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="F135" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I135" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J135" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K135" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="L135" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="P135" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="R135" s="87" t="inlineStr">
+        <is>
+          <t>09/03/25</t>
+        </is>
+      </c>
+      <c r="S135" s="90" t="n">
+        <v>45915</v>
+      </c>
+      <c r="U135" s="90" t="n">
+        <v>46660</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="C136" s="87" t="inlineStr">
+        <is>
+          <t>Reyes, Lenyn</t>
+        </is>
+      </c>
+      <c r="E136" s="87" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F136" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I136" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J136" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K136" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L136" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" s="89" t="n">
+        <v>35</v>
+      </c>
+      <c r="O136" s="89" t="n">
+        <v>1485</v>
+      </c>
+      <c r="P136" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="Q136" s="89" t="n">
+        <v>1450</v>
+      </c>
+      <c r="R136" s="87" t="inlineStr">
+        <is>
+          <t>02/25/25</t>
+        </is>
+      </c>
+      <c r="S136" s="90" t="n">
+        <v>45715</v>
+      </c>
+      <c r="U136" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="C137" s="87" t="inlineStr">
+        <is>
+          <t>Nance (RACB), Moesha</t>
+        </is>
+      </c>
+      <c r="E137" s="87" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="F137" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I137" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J137" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K137" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L137" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="P137" s="89" t="n">
+        <v>1238</v>
+      </c>
+      <c r="Q137" s="89" t="n">
+        <v>112</v>
+      </c>
+      <c r="R137" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="S137" s="90" t="n">
+        <v>45593</v>
+      </c>
+      <c r="U137" s="90" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="C138" s="87" t="inlineStr">
+        <is>
+          <t>Velez, Juan</t>
+        </is>
+      </c>
+      <c r="E138" s="87" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="F138" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I138" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J138" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K138" s="89" t="n">
+        <v>950</v>
+      </c>
+      <c r="L138" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" s="89" t="n">
+        <v>950</v>
+      </c>
+      <c r="P138" s="89" t="n">
+        <v>475</v>
+      </c>
+      <c r="Q138" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R138" s="87" t="inlineStr">
+        <is>
+          <t>06/01/25</t>
+        </is>
+      </c>
+      <c r="S138" s="90" t="n">
+        <v>42522</v>
+      </c>
+      <c r="U138" s="90" t="n">
+        <v>46173</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="C139" s="87" t="inlineStr">
+        <is>
+          <t>Ivy (BEL), Tiera</t>
+        </is>
+      </c>
+      <c r="E139" s="87" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="F139" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I139" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J139" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K139" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="L139" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="P139" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q139" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="R139" s="87" t="inlineStr">
+        <is>
+          <t>04/08/25</t>
+        </is>
+      </c>
+      <c r="S139" s="90" t="n">
+        <v>45757</v>
+      </c>
+      <c r="T139" s="90" t="n">
+        <v>46295</v>
+      </c>
+      <c r="U139" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="C140" s="87" t="inlineStr">
+        <is>
+          <t>Miller, Victoria</t>
+        </is>
+      </c>
+      <c r="E140" s="87" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F140" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I140" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J140" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K140" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="L140" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" s="89" t="n">
+        <v>1075</v>
+      </c>
+      <c r="P140" s="89" t="n">
+        <v>1050</v>
+      </c>
+      <c r="Q140" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="R140" s="87" t="inlineStr">
+        <is>
+          <t>01/01/25</t>
+        </is>
+      </c>
+      <c r="S140" s="90" t="n">
+        <v>45289</v>
+      </c>
+      <c r="T140" s="90" t="n">
+        <v>46295</v>
+      </c>
+      <c r="U140" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="C141" s="87" t="inlineStr">
+        <is>
+          <t>Thomas, Alisa</t>
+        </is>
+      </c>
+      <c r="E141" s="87" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F141" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I141" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J141" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K141" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="L141" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" s="89" t="n">
+        <v>1500</v>
+      </c>
+      <c r="P141" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="Q141" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="R141" s="87" t="inlineStr">
+        <is>
+          <t>07/01/25</t>
+        </is>
+      </c>
+      <c r="S141" s="90" t="n">
+        <v>45474</v>
+      </c>
+      <c r="U141" s="90" t="n">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="C142" s="87" t="inlineStr">
+        <is>
+          <t>Lopez, Carlos</t>
+        </is>
+      </c>
+      <c r="E142" s="87" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="F142" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I142" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J142" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K142" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L142" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P142" s="89" t="n">
+        <v>750</v>
+      </c>
+      <c r="Q142" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="R142" s="87" t="inlineStr">
+        <is>
+          <t>05/01/24</t>
+        </is>
+      </c>
+      <c r="S142" s="90" t="n">
+        <v>43987</v>
+      </c>
+      <c r="U142" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" s="87" t="inlineStr">
+        <is>
+          <t>Peete Sr, Tyshone</t>
+        </is>
+      </c>
+      <c r="E143" s="87" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="F143" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I143" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J143" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K143" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L143" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="89" t="n">
+        <v>35</v>
+      </c>
+      <c r="O143" s="89" t="n">
+        <v>1435</v>
+      </c>
+      <c r="P143" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q143" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R143" s="87" t="inlineStr">
+        <is>
+          <t>03/25/25</t>
+        </is>
+      </c>
+      <c r="S143" s="90" t="n">
+        <v>45744</v>
+      </c>
+      <c r="U143" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="C144" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E144" s="87" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="F144" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I144" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J144" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K144" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L144" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="M144" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="C145" s="87" t="inlineStr">
+        <is>
+          <t>Caceres (RACB), Carmen</t>
+        </is>
+      </c>
+      <c r="E145" s="87" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="F145" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I145" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J145" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K145" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L145" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P145" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q145" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R145" s="87" t="inlineStr">
+        <is>
+          <t>02/01/24</t>
+        </is>
+      </c>
+      <c r="S145" s="90" t="n">
+        <v>41670</v>
+      </c>
+      <c r="U145" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="C146" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E146" s="87" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F146" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I146" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J146" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K146" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L146" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="M146" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="C147" s="87" t="inlineStr">
+        <is>
+          <t>Miranda, Yamilex</t>
+        </is>
+      </c>
+      <c r="E147" s="87" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="F147" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I147" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J147" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K147" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="L147" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="P147" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="Q147" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="R147" s="87" t="inlineStr">
+        <is>
+          <t>12/10/25</t>
+        </is>
+      </c>
+      <c r="S147" s="90" t="n">
+        <v>46023</v>
+      </c>
+      <c r="U147" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="C148" s="87" t="inlineStr">
+        <is>
+          <t>Robbins, Dewan</t>
+        </is>
+      </c>
+      <c r="E148" s="87" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="F148" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I148" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J148" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K148" s="89" t="n">
+        <v>1145</v>
+      </c>
+      <c r="L148" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="89" t="n">
+        <v>1145</v>
+      </c>
+      <c r="P148" s="89" t="n">
+        <v>1145</v>
+      </c>
+      <c r="Q148" s="89" t="n">
+        <v>1145</v>
+      </c>
+      <c r="R148" s="87" t="inlineStr">
+        <is>
+          <t>02/28/25</t>
+        </is>
+      </c>
+      <c r="S148" s="90" t="n">
+        <v>45719</v>
+      </c>
+      <c r="U148" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="C149" s="87" t="inlineStr">
+        <is>
+          <t>Hernandez (RACB), Vanessa</t>
+        </is>
+      </c>
+      <c r="E149" s="87" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="F149" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/ 1Bath</t>
+        </is>
+      </c>
+      <c r="I149" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J149" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K149" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="L149" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="P149" s="89" t="n">
+        <v>1300</v>
+      </c>
+      <c r="Q149" s="89" t="n">
+        <v>175</v>
+      </c>
+      <c r="R149" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="S149" s="90" t="n">
+        <v>45344</v>
+      </c>
+      <c r="T149" s="90" t="n">
+        <v>46296</v>
+      </c>
+      <c r="U149" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="C150" s="87" t="inlineStr">
+        <is>
+          <t>Edwards (BEL), Maureen</t>
+        </is>
+      </c>
+      <c r="E150" s="87" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F150" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I150" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J150" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K150" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L150" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O150" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P150" s="89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Q150" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R150" s="87" t="inlineStr">
+        <is>
+          <t>02/01/25</t>
+        </is>
+      </c>
+      <c r="S150" s="90" t="n">
+        <v>45314</v>
+      </c>
+      <c r="U150" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="C151" s="87" t="inlineStr">
+        <is>
+          <t>Williams, Jamelle</t>
+        </is>
+      </c>
+      <c r="E151" s="87" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="F151" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I151" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J151" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K151" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L151" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P151" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q151" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R151" s="87" t="inlineStr">
+        <is>
+          <t>12/17/25</t>
+        </is>
+      </c>
+      <c r="S151" s="90" t="n">
+        <v>46023</v>
+      </c>
+      <c r="U151" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="C152" s="87" t="inlineStr">
+        <is>
+          <t>Patterson, Christalee</t>
+        </is>
+      </c>
+      <c r="E152" s="87" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="F152" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I152" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J152" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K152" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L152" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P152" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="Q152" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="R152" s="87" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
+      <c r="S152" s="90" t="n">
+        <v>46204</v>
+      </c>
+      <c r="U152" s="90" t="n">
+        <v>46568</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="C153" s="87" t="inlineStr">
+        <is>
+          <t>Tchassi Fotsing (JER), Gabriel</t>
+        </is>
+      </c>
+      <c r="E153" s="87" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="F153" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I153" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J153" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K153" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="L153" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="P153" s="89" t="n">
+        <v>1375</v>
+      </c>
+      <c r="Q153" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R153" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="S153" s="90" t="n">
+        <v>45331</v>
+      </c>
+      <c r="U153" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="C154" s="87" t="inlineStr">
+        <is>
+          <t>&lt;VACANT&gt;</t>
+        </is>
+      </c>
+      <c r="E154" s="87" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="F154" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I154" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J154" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K154" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="L154" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="M154" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" s="89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="C155" s="87" t="inlineStr">
+        <is>
+          <t>Villamil (RACB), Karen</t>
+        </is>
+      </c>
+      <c r="E155" s="87" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="F155" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I155" s="88" t="n">
+        <v>1541</v>
+      </c>
+      <c r="J155" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K155" s="89" t="n">
+        <v>1275</v>
+      </c>
+      <c r="L155" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O155" s="89" t="n">
+        <v>1325</v>
+      </c>
+      <c r="P155" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R155" s="87" t="inlineStr">
+        <is>
+          <t>05/01/25</t>
+        </is>
+      </c>
+      <c r="S155" s="90" t="n">
+        <v>43435</v>
+      </c>
+      <c r="U155" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="C156" s="87" t="inlineStr">
+        <is>
+          <t>Kawaya, Cynthia</t>
+        </is>
+      </c>
+      <c r="E156" s="87" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F156" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed 1.5 Bath</t>
+        </is>
+      </c>
+      <c r="I156" s="88" t="n">
+        <v>1541</v>
+      </c>
+      <c r="J156" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="K156" s="89" t="n">
+        <v>1525</v>
+      </c>
+      <c r="L156" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" s="89" t="n">
+        <v>1525</v>
+      </c>
+      <c r="P156" s="89" t="n">
+        <v>1495</v>
+      </c>
+      <c r="Q156" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R156" s="87" t="inlineStr">
+        <is>
+          <t>01/01/25</t>
+        </is>
+      </c>
+      <c r="S156" s="90" t="n">
+        <v>44900</v>
+      </c>
+      <c r="U156" s="90" t="n">
+        <v>46387</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="C157" s="87" t="inlineStr">
+        <is>
+          <t>Lopez (RACB), Erica</t>
+        </is>
+      </c>
+      <c r="E157" s="87" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="F157" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I157" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J157" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K157" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L157" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" s="89" t="n">
+        <v>50</v>
+      </c>
+      <c r="O157" s="89" t="n">
+        <v>1150</v>
+      </c>
+      <c r="P157" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q157" s="89" t="n">
+        <v>84</v>
+      </c>
+      <c r="R157" s="87" t="inlineStr">
+        <is>
+          <t>12/01/24</t>
+        </is>
+      </c>
+      <c r="S157" s="90" t="n">
+        <v>43420</v>
+      </c>
+      <c r="U157" s="90" t="n">
+        <v>46356</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="C158" s="87" t="inlineStr">
+        <is>
+          <t>Banks, Najah</t>
+        </is>
+      </c>
+      <c r="E158" s="87" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="F158" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I158" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J158" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K158" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L158" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P158" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="Q158" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="R158" s="87" t="inlineStr">
+        <is>
+          <t>01/09/26</t>
+        </is>
+      </c>
+      <c r="S158" s="90" t="n">
+        <v>46054</v>
+      </c>
+      <c r="U158" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="C159" s="87" t="inlineStr">
+        <is>
+          <t>Pierantoni-Vazquez, Jennifer</t>
+        </is>
+      </c>
+      <c r="E159" s="87" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="F159" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I159" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J159" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K159" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L159" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="P159" s="89" t="n">
+        <v>695</v>
+      </c>
+      <c r="Q159" s="89" t="n">
+        <v>75</v>
+      </c>
+      <c r="R159" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="S159" s="90" t="n">
+        <v>43160</v>
+      </c>
+      <c r="U159" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="C160" s="87" t="inlineStr">
+        <is>
+          <t>Phillips, Thomas</t>
+        </is>
+      </c>
+      <c r="E160" s="87" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="F160" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I160" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J160" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K160" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L160" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P160" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q160" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="R160" s="87" t="inlineStr">
+        <is>
+          <t>01/08/26</t>
+        </is>
+      </c>
+      <c r="S160" s="90" t="n">
+        <v>46037</v>
+      </c>
+      <c r="U160" s="90" t="n">
+        <v>46418</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="C161" s="87" t="inlineStr">
+        <is>
+          <t>Harmon, Ashley</t>
+        </is>
+      </c>
+      <c r="E161" s="87" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="F161" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I161" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J161" s="89" t="n">
+        <v>1475</v>
+      </c>
+      <c r="K161" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L161" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" s="89" t="n">
+        <v>1125</v>
+      </c>
+      <c r="P161" s="89" t="n">
+        <v>1360</v>
+      </c>
+      <c r="Q161" s="89" t="n">
+        <v>100</v>
+      </c>
+      <c r="R161" s="87" t="inlineStr">
+        <is>
+          <t>03/01/25</t>
+        </is>
+      </c>
+      <c r="S161" s="90" t="n">
+        <v>42074</v>
+      </c>
+      <c r="U161" s="90" t="n">
+        <v>46446</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="C162" s="87" t="inlineStr">
+        <is>
+          <t>Services, TSI, Transitional</t>
+        </is>
+      </c>
+      <c r="E162" s="87" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="F162" s="87" t="inlineStr">
+        <is>
+          <t>1 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I162" s="88" t="n">
+        <v>1149</v>
+      </c>
+      <c r="J162" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="K162" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="L162" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" s="89" t="n">
+        <v>1195</v>
+      </c>
+      <c r="P162" s="89" t="n">
+        <v>1100</v>
+      </c>
+      <c r="Q162" s="89" t="n">
+        <v>95</v>
+      </c>
+      <c r="R162" s="87" t="inlineStr">
+        <is>
+          <t>04/01/25</t>
+        </is>
+      </c>
+      <c r="S162" s="90" t="n">
+        <v>45364</v>
+      </c>
+      <c r="U162" s="90" t="n">
+        <v>46477</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="C163" s="87" t="inlineStr">
+        <is>
+          <t>Matos (RACB), Jade</t>
+        </is>
+      </c>
+      <c r="E163" s="87" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="F163" s="87" t="inlineStr">
+        <is>
+          <t>3 Bed/1Bath FP</t>
+        </is>
+      </c>
+      <c r="I163" s="88" t="n">
+        <v>1521</v>
+      </c>
+      <c r="J163" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K163" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L163" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="P163" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="Q163" s="89" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R163" s="87" t="inlineStr">
+        <is>
+          <t>04/29/26</t>
+        </is>
+      </c>
+      <c r="S163" s="90" t="n">
+        <v>46143</v>
+      </c>
+      <c r="U163" s="90" t="n">
+        <v>46507</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="C164" s="87" t="inlineStr">
+        <is>
+          <t>Brown, Angel</t>
+        </is>
+      </c>
+      <c r="E164" s="87" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F164" s="87" t="inlineStr">
+        <is>
+          <t>2 Bed 1 Bath</t>
+        </is>
+      </c>
+      <c r="I164" s="88" t="n">
+        <v>1334</v>
+      </c>
+      <c r="J164" s="89" t="n">
+        <v>1350</v>
+      </c>
+      <c r="K164" s="89" t="n">
+        <v>925</v>
+      </c>
+      <c r="L164" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="89" t="n">
+        <v>925</v>
+      </c>
+      <c r="P164" s="89" t="n">
+        <v>575</v>
+      </c>
+      <c r="Q164" s="89" t="n">
+        <v>25</v>
+      </c>
+      <c r="R164" s="87" t="inlineStr">
+        <is>
+          <t>11/01/25</t>
+        </is>
+      </c>
+      <c r="S164" s="90" t="n">
+        <v>40848</v>
+      </c>
+      <c r="U164" s="90" t="n">
+        <v>46691</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="I165" s="88" t="n">
+        <v>213124</v>
+      </c>
+      <c r="J165" s="89" t="n">
+        <v>211875</v>
+      </c>
+      <c r="K165" s="89" t="n">
+        <v>197636</v>
+      </c>
+      <c r="L165" s="89" t="n">
+        <v>18250</v>
+      </c>
+      <c r="M165" s="89" t="n">
+        <v>1635</v>
+      </c>
+      <c r="O165" s="89" t="n">
+        <v>181021</v>
+      </c>
+      <c r="P165" s="89" t="n">
+        <v>123235.5</v>
+      </c>
+      <c r="Q165" s="89" t="n">
+        <v>86293</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Totals for </t>
+        </is>
+      </c>
+      <c r="D166" s="87" t="inlineStr">
+        <is>
+          <t>Hertel Homes</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="I169" s="87" t="inlineStr">
+        <is>
+          <t>Sq Ft</t>
+        </is>
+      </c>
+      <c r="J169" s="87" t="inlineStr">
+        <is>
+          <t>Market 
+Rent</t>
+        </is>
+      </c>
+      <c r="K169" s="87" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="L169" s="87" t="inlineStr">
+        <is>
+          <t>Vacancy 
+Loss</t>
+        </is>
+      </c>
+      <c r="M169" s="87" t="inlineStr">
+        <is>
+          <t>Misc 
+Charges</t>
+        </is>
+      </c>
+      <c r="O169" s="87" t="inlineStr">
+        <is>
+          <t>Total 
+Charges</t>
+        </is>
+      </c>
+      <c r="P169" s="87" t="inlineStr">
+        <is>
+          <t>Security 
+Deposit</t>
+        </is>
+      </c>
+      <c r="Q169" s="87" t="inlineStr">
+        <is>
+          <t>Increase 
+Amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="I170" s="88" t="n">
+        <v>213124</v>
+      </c>
+      <c r="J170" s="89" t="n">
+        <v>211875</v>
+      </c>
+      <c r="K170" s="89" t="n">
+        <v>197636</v>
+      </c>
+      <c r="L170" s="89" t="n">
+        <v>18250</v>
+      </c>
+      <c r="M170" s="89" t="n">
+        <v>1635</v>
+      </c>
+      <c r="O170" s="89" t="n">
+        <v>181021</v>
+      </c>
+      <c r="P170" s="89" t="n">
+        <v>123235.5</v>
+      </c>
+      <c r="Q170" s="89" t="n">
+        <v>86293</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="87" t="inlineStr">
+        <is>
+          <t>Report Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="87" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="N174" s="87" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="87" t="inlineStr">
+        <is>
+          <t>Total Possible Rent</t>
+        </is>
+      </c>
+      <c r="N175" s="87" t="inlineStr">
+        <is>
+          <t>197,636.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="87" t="inlineStr">
+        <is>
+          <t>Vacancy Rent</t>
+        </is>
+      </c>
+      <c r="N176" s="87" t="inlineStr">
+        <is>
+          <t>18,250.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="87" t="inlineStr">
+        <is>
+          <t>Occupied Unit Rent</t>
+        </is>
+      </c>
+      <c r="N177" s="87" t="inlineStr">
+        <is>
+          <t>179,386.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="87" t="inlineStr">
+        <is>
+          <t># of Units</t>
+        </is>
+      </c>
+      <c r="N178" s="87" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="87" t="inlineStr">
+        <is>
+          <t>Vacant Units</t>
+        </is>
+      </c>
+      <c r="N179" s="87" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="87" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="N180" s="87" t="inlineStr">
+        <is>
+          <t>91.14%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="660">
+    <mergeCell ref="F116:G116"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="U128:V128"/>
+    <mergeCell ref="F103:G103"/>
+    <mergeCell ref="N180:V180"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="F108:G108"/>
+    <mergeCell ref="F143:G143"/>
+    <mergeCell ref="M79:N79"/>
+    <mergeCell ref="U65:V65"/>
+    <mergeCell ref="F118:G118"/>
+    <mergeCell ref="C79:D79"/>
+    <mergeCell ref="U136:V136"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="C121:D121"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M99:N99"/>
+    <mergeCell ref="F70:G70"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="M74:N74"/>
+    <mergeCell ref="U131:V131"/>
+    <mergeCell ref="N177:V177"/>
+    <mergeCell ref="F134:G134"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="U146:V146"/>
+    <mergeCell ref="F121:G121"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="U83:V83"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="M150:N150"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="U85:V85"/>
+    <mergeCell ref="M50:N50"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="F162:G162"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="C92:D92"/>
+    <mergeCell ref="M92:N92"/>
+    <mergeCell ref="M152:N152"/>
+    <mergeCell ref="U78:V78"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="U124:V124"/>
+    <mergeCell ref="C97:D97"/>
+    <mergeCell ref="U80:V80"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F126:G126"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="F109:G109"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="M105:N105"/>
+    <mergeCell ref="C123:D123"/>
+    <mergeCell ref="U71:V71"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="M120:N120"/>
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="F111:G111"/>
+    <mergeCell ref="U58:V58"/>
+    <mergeCell ref="M163:N163"/>
+    <mergeCell ref="M101:N101"/>
+    <mergeCell ref="N175:V175"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="M76:N76"/>
+    <mergeCell ref="U73:V73"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="M165:N165"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="U137:V137"/>
+    <mergeCell ref="M115:N115"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="F137:G137"/>
+    <mergeCell ref="U84:V84"/>
+    <mergeCell ref="U155:V155"/>
+    <mergeCell ref="U149:V149"/>
+    <mergeCell ref="F124:G124"/>
+    <mergeCell ref="C128:D128"/>
+    <mergeCell ref="C113:D113"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="F164:G164"/>
+    <mergeCell ref="F139:G139"/>
+    <mergeCell ref="C100:D100"/>
+    <mergeCell ref="U86:V86"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="U151:V151"/>
+    <mergeCell ref="F114:G114"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="C142:D142"/>
+    <mergeCell ref="N178:V178"/>
+    <mergeCell ref="U150:V150"/>
+    <mergeCell ref="C80:D80"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="C129:D129"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="M95:N95"/>
+    <mergeCell ref="U152:V152"/>
+    <mergeCell ref="M89:N89"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M97:N97"/>
+    <mergeCell ref="F117:G117"/>
+    <mergeCell ref="F92:G92"/>
+    <mergeCell ref="C131:D131"/>
+    <mergeCell ref="F119:G119"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="U35:V35"/>
+    <mergeCell ref="F69:G69"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="F112:G112"/>
+    <mergeCell ref="A172:U172"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="M113:N113"/>
+    <mergeCell ref="U99:V99"/>
+    <mergeCell ref="N176:V176"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="F127:G127"/>
+    <mergeCell ref="C88:D88"/>
+    <mergeCell ref="M123:N123"/>
+    <mergeCell ref="U74:V74"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="M110:N110"/>
+    <mergeCell ref="U163:V163"/>
+    <mergeCell ref="U101:V101"/>
+    <mergeCell ref="U76:V76"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C117:D117"/>
+    <mergeCell ref="C55:D55"/>
+    <mergeCell ref="M108:N108"/>
+    <mergeCell ref="F145:G145"/>
+    <mergeCell ref="C115:D115"/>
+    <mergeCell ref="F38:G38"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C150:D150"/>
+    <mergeCell ref="F140:G140"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C144:D144"/>
+    <mergeCell ref="U92:V92"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="U54:V54"/>
+    <mergeCell ref="C81:D81"/>
+    <mergeCell ref="F82:G82"/>
+    <mergeCell ref="M103:N103"/>
+    <mergeCell ref="M159:N159"/>
+    <mergeCell ref="M134:N134"/>
+    <mergeCell ref="U94:V94"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="M121:N121"/>
+    <mergeCell ref="A3:V3"/>
+    <mergeCell ref="M96:N96"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="M161:N161"/>
+    <mergeCell ref="U158:V158"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="M111:N111"/>
+    <mergeCell ref="M98:N98"/>
+    <mergeCell ref="F158:G158"/>
+    <mergeCell ref="U105:V105"/>
+    <mergeCell ref="F133:G133"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="U120:V120"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="F160:G160"/>
+    <mergeCell ref="U107:V107"/>
+    <mergeCell ref="F135:G135"/>
+    <mergeCell ref="U57:V57"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="F122:G122"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="F153:G153"/>
+    <mergeCell ref="U100:V100"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="C76:D76"/>
+    <mergeCell ref="M124:N124"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="U115:V115"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="C119:D119"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="U42:V42"/>
+    <mergeCell ref="M116:N116"/>
+    <mergeCell ref="U102:V102"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="U148:V148"/>
+    <mergeCell ref="M126:N126"/>
+    <mergeCell ref="C158:D158"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="F148:G148"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="F146:G146"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="M142:N142"/>
+    <mergeCell ref="M129:N129"/>
+    <mergeCell ref="U108:V108"/>
+    <mergeCell ref="F83:G83"/>
+    <mergeCell ref="C147:D147"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="U95:V95"/>
+    <mergeCell ref="M144:N144"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="U159:V159"/>
+    <mergeCell ref="M137:N137"/>
+    <mergeCell ref="U97:V97"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="U47:V47"/>
+    <mergeCell ref="M164:N164"/>
+    <mergeCell ref="U161:V161"/>
+    <mergeCell ref="M139:N139"/>
+    <mergeCell ref="C71:D71"/>
+    <mergeCell ref="M41:N41"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A177:M177"/>
+    <mergeCell ref="U121:V121"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="F161:G161"/>
+    <mergeCell ref="F136:G136"/>
+    <mergeCell ref="U129:V129"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="M66:N66"/>
+    <mergeCell ref="U123:V123"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="A179:M179"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="U110:V110"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="U50:V50"/>
+    <mergeCell ref="U44:V44"/>
+    <mergeCell ref="C77:D77"/>
+    <mergeCell ref="M130:N130"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="M68:N68"/>
+    <mergeCell ref="M117:N117"/>
+    <mergeCell ref="M55:N55"/>
+    <mergeCell ref="C160:D160"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="M67:N67"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="A180:M180"/>
+    <mergeCell ref="M132:N132"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="U45:V45"/>
+    <mergeCell ref="M119:N119"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="M69:N69"/>
+    <mergeCell ref="F154:G154"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F156:G156"/>
+    <mergeCell ref="U103:V103"/>
+    <mergeCell ref="U134:V134"/>
+    <mergeCell ref="M81:N81"/>
+    <mergeCell ref="M37:N37"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="F155:G155"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F93:G93"/>
+    <mergeCell ref="F149:G149"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="M145:N145"/>
+    <mergeCell ref="U142:V142"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="U55:V55"/>
+    <mergeCell ref="C125:D125"/>
+    <mergeCell ref="C161:D161"/>
+    <mergeCell ref="F151:G151"/>
+    <mergeCell ref="U98:V98"/>
+    <mergeCell ref="M147:N147"/>
+    <mergeCell ref="M38:N38"/>
+    <mergeCell ref="M122:N122"/>
+    <mergeCell ref="C154:D154"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C156:D156"/>
+    <mergeCell ref="C74:D74"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="F104:G104"/>
+    <mergeCell ref="C103:D103"/>
+    <mergeCell ref="M94:N94"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C118:D118"/>
+    <mergeCell ref="U66:V66"/>
+    <mergeCell ref="M140:N140"/>
+    <mergeCell ref="U126:V126"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F106:G106"/>
+    <mergeCell ref="U53:V53"/>
+    <mergeCell ref="M158:N158"/>
+    <mergeCell ref="M77:N77"/>
+    <mergeCell ref="M133:N133"/>
+    <mergeCell ref="U130:V130"/>
+    <mergeCell ref="U68:V68"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="U117:V117"/>
+    <mergeCell ref="M160:N160"/>
+    <mergeCell ref="M135:N135"/>
+    <mergeCell ref="F130:G130"/>
+    <mergeCell ref="M72:N72"/>
+    <mergeCell ref="C96:D96"/>
+    <mergeCell ref="F157:G157"/>
+    <mergeCell ref="F132:G132"/>
+    <mergeCell ref="U79:V79"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="U144:V144"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="U119:V119"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="C98:D98"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="U81:V81"/>
+    <mergeCell ref="C89:D89"/>
+    <mergeCell ref="C116:D116"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="M88:N88"/>
+    <mergeCell ref="M148:N148"/>
+    <mergeCell ref="U145:V145"/>
+    <mergeCell ref="M82:N82"/>
+    <mergeCell ref="M153:N153"/>
+    <mergeCell ref="U139:V139"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="C93:D93"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="C164:D164"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="U122:V122"/>
+    <mergeCell ref="F125:G125"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="M85:N85"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F105:G105"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="F120:G120"/>
+    <mergeCell ref="U67:V67"/>
+    <mergeCell ref="M141:N141"/>
+    <mergeCell ref="U138:V138"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="U132:V132"/>
+    <mergeCell ref="F107:G107"/>
+    <mergeCell ref="U5:V5"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="C83:D83"/>
+    <mergeCell ref="U69:V69"/>
+    <mergeCell ref="M143:N143"/>
+    <mergeCell ref="M118:N118"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="N179:V179"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="C137:D137"/>
+    <mergeCell ref="C124:D124"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="U160:V160"/>
+    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="U147:V147"/>
+    <mergeCell ref="U87:V87"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="C132:D132"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="M154:N154"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="U89:V89"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="M91:N91"/>
+    <mergeCell ref="U82:V82"/>
+    <mergeCell ref="M156:N156"/>
+    <mergeCell ref="M155:N155"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="M93:N93"/>
+    <mergeCell ref="F64:G64"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="F128:G128"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="U77:V77"/>
+    <mergeCell ref="C85:D85"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="C112:D112"/>
+    <mergeCell ref="M109:N109"/>
+    <mergeCell ref="M169:N169"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="C84:D84"/>
+    <mergeCell ref="U141:V141"/>
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="U135:V135"/>
+    <mergeCell ref="F110:G110"/>
+    <mergeCell ref="M75:N75"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C114:D114"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="U37:V37"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="U72:V72"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="U143:V143"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="M104:N104"/>
+    <mergeCell ref="F141:G141"/>
+    <mergeCell ref="M106:N106"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="U113:V113"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="U88:V88"/>
+    <mergeCell ref="M162:N162"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="U153:V153"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C104:D104"/>
+    <mergeCell ref="U90:V90"/>
+    <mergeCell ref="F65:G65"/>
+    <mergeCell ref="M170:N170"/>
+    <mergeCell ref="U27:V27"/>
+    <mergeCell ref="M157:N157"/>
+    <mergeCell ref="U154:V154"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="C99:D99"/>
+    <mergeCell ref="F129:G129"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="C130:D130"/>
+    <mergeCell ref="U116:V116"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="F131:G131"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="M61:N61"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="U118:V118"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="C159:D159"/>
+    <mergeCell ref="C122:D122"/>
+    <mergeCell ref="C153:D153"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="C72:D72"/>
+    <mergeCell ref="M125:N125"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="U38:V38"/>
+    <mergeCell ref="M112:N112"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A175:M175"/>
+    <mergeCell ref="M127:N127"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="M114:N114"/>
+    <mergeCell ref="F68:G68"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="M107:N107"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="U96:V96"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="F142:G142"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="C146:D146"/>
+    <mergeCell ref="M138:N138"/>
+    <mergeCell ref="C41:D41"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="C56:D56"/>
+    <mergeCell ref="F144:G144"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="U162:V162"/>
+    <mergeCell ref="U91:V91"/>
+    <mergeCell ref="D166:H166"/>
+    <mergeCell ref="U156:V156"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="C120:D120"/>
+    <mergeCell ref="U106:V106"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="M36:N36"/>
+    <mergeCell ref="U93:V93"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="U164:V164"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="C149:D149"/>
+    <mergeCell ref="M100:N100"/>
+    <mergeCell ref="U157:V157"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="M62:N62"/>
+    <mergeCell ref="N174:V174"/>
+    <mergeCell ref="M102:N102"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="U109:V109"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="U59:V59"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="U46:V46"/>
+    <mergeCell ref="U111:V111"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="M64:N64"/>
+    <mergeCell ref="U61:V61"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="U104:V104"/>
+    <mergeCell ref="U48:V48"/>
+    <mergeCell ref="F138:G138"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F76:G76"/>
+    <mergeCell ref="A176:M176"/>
+    <mergeCell ref="M128:N128"/>
+    <mergeCell ref="F94:G94"/>
+    <mergeCell ref="U41:V41"/>
+    <mergeCell ref="M65:N65"/>
+    <mergeCell ref="U56:V56"/>
+    <mergeCell ref="A178:M178"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="U43:V43"/>
+    <mergeCell ref="F150:G150"/>
+    <mergeCell ref="C91:D91"/>
+    <mergeCell ref="F152:G152"/>
+    <mergeCell ref="C82:D82"/>
+    <mergeCell ref="C57:D57"/>
+    <mergeCell ref="U114:V114"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="M146:N146"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="F147:G147"/>
+    <mergeCell ref="M83:N83"/>
+    <mergeCell ref="C151:D151"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="U34:V34"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="U49:V49"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="M39:N39"/>
+    <mergeCell ref="U36:V36"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C152:D152"/>
+    <mergeCell ref="M78:N78"/>
+    <mergeCell ref="C75:D75"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="F163:G163"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="U125:V125"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="U112:V112"/>
+    <mergeCell ref="F115:G115"/>
+    <mergeCell ref="U62:V62"/>
+    <mergeCell ref="M136:N136"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="U127:V127"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="U64:V64"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="M71:N71"/>
+    <mergeCell ref="M131:N131"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="C101:D101"/>
+    <mergeCell ref="U140:V140"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F95:G95"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="F113:G113"/>
+    <mergeCell ref="F32:G32"/>
+    <mergeCell ref="F159:G159"/>
+    <mergeCell ref="M84:N84"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="U75:V75"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M149:N149"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="M86:N86"/>
+    <mergeCell ref="M80:N80"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="M151:N151"/>
+    <mergeCell ref="A166:C166"/>
+    <mergeCell ref="A174:M174"/>
+    <mergeCell ref="U52:V52"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="U39:V39"/>
+    <mergeCell ref="U133:V133"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F123:G123"/>
+    <mergeCell ref="C78:D78"/>
+    <mergeCell ref="F44:G44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>